--- a/data/trans_orig/IP16A06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A06-Estudios-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19016</t>
+          <t>18414</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>16141</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37076</t>
+          <t>37123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41713</t>
+          <t>41709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>555</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75668</t>
+          <t>75599</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82594</t>
+          <t>82745</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87116</t>
+          <t>87114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>160974</t>
+          <t>161002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167081</t>
+          <t>167182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9719</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119513</t>
+          <t>119409</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124705</t>
+          <t>124708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136452</t>
+          <t>136287</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142012</t>
+          <t>142000</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>258039</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>266231</t>
+          <t>265930</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3668</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19918</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24880</t>
+          <t>24870</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19698</t>
+          <t>19184</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42252</t>
+          <t>42234</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47715</t>
+          <t>47710</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111047</t>
+          <t>111495</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>119304</t>
+          <t>118783</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>232948</t>
+          <t>233138</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>238355</t>
+          <t>238359</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40800</t>
+          <t>41453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88002</t>
+          <t>87517</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>179274</t>
+          <t>179389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186191</t>
+          <t>186176</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>184212</t>
+          <t>184876</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190761</t>
+          <t>190787</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>367557</t>
+          <t>367407</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>375823</t>
+          <t>375844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28501</t>
+          <t>28548</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>523</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>103034</t>
+          <t>103250</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93574</t>
+          <t>93384</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>198574</t>
+          <t>199014</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>203073</t>
+          <t>203078</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34890</t>
+          <t>34354</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>71730</t>
+          <t>72128</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>584</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158630</t>
+          <t>158493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142523</t>
+          <t>143058</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147533</t>
+          <t>147541</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304363</t>
+          <t>304097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>309548</t>
+          <t>309554</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/IP16A06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A06-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4089</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20,19%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3634</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3059</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1343</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4117</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>593</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18915</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16169</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>79,81%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21450</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18414</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>18989</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,29%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,52%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>86,12%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18915</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16141</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,37%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>79,68%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>60</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37123</t>
+          <t>37178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41709</t>
+          <t>41712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1871</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4943</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1445</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5108</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4812</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1871</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4924</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>85798</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82726</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>87116</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>79262</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>75599</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>75895</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,21%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,67%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,04%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85798</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>82745</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>87114</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>94,38%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>249</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>161002</t>
+          <t>160951</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167182</t>
+          <t>167163</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>22551</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6991</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2043</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5896</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5677</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3213</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1193</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6906</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>139980</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>136202</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>141944</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,76%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,12%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>123262</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>119409</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>124708</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>119628</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>124709</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,52%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>139980</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>136287</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>142000</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,18%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>396</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>258039</t>
+          <t>258341</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>265930</t>
+          <t>266030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,72 +2325,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,71%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2129</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>653</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5465</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5353</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,34%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>2,56%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>21,41%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3668</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -2438,74 +2438,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22245</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19948</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,29%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>23394</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20058</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>20170</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>24870</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,66%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>78,59%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>79,03%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>97,44%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>22245</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>19184</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>83,95%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>65</t>
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42234</t>
+          <t>42023</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47710</t>
+          <t>47700</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>25523</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>25523</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>25523</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4114</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4353</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1338</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4611</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -2781,74 +2781,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>122056</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>118594</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>123394</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>114791</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>111495</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>111256</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>115609</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,29%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,23%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>122056</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>118783</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>123394</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,26%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>341</t>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>233138</t>
+          <t>233198</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>238359</t>
+          <t>238354</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>123394</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>123394</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>123394</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>115609</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>115609</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>115609</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>123394</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>123394</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>123394</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,107 +3011,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3724</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>722</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3779</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3668</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3574</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -3124,74 +3124,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>44510</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>41508</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,77%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>45859</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>44510</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>41453</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>91,65%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>126</t>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87517</t>
+          <t>87423</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>45859</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>45859</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>45859</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3359,67 +3359,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6824</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>2947</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>816</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7603</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7263</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6602</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -3467,72 +3467,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>188811</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>184654</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>190789</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>184045</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>179389</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>186176</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>179729</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>186194</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,42%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>188811</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>184876</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>190787</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>367407</t>
+          <t>367090</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>375844</t>
+          <t>375839</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>186992</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3928,107 +3928,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3800</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3252</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>17,25%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3164</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3082</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -4041,74 +4041,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18239</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15056</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15604</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>18856</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,73%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>79,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>82,75%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>44</t>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28548</t>
+          <t>28466</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>18856</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>18856</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>18856</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,107 +4271,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3827</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2660</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2665</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1738</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4308</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4610</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1738</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4587</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -4384,107 +4384,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96478</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>93865</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>97692</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,76%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>105386</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>103250</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>103245</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>105910</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,51%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,49%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,48%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96478</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>93384</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>97692</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,59%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>201863</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>198991</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>203601</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>97,74%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>201863</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>199014</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>203078</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>97,75%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>97692</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>97692</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>97692</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105910</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105910</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105910</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>97692</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>97692</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>97692</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4614,107 +4614,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3266</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3305</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2903</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>8,78%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3301</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -4727,74 +4727,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>37013</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34393</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>37770</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>37013</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>34354</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,29%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>91,22%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>109</t>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72128</t>
+          <t>72526</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>37770</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>37770</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>37770</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5531</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4043</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3951</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5067</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -5070,74 +5070,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>146266</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>142594</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>147536</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>161395</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>158493</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>158585</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>146266</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>143058</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>147541</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>455</t>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304097</t>
+          <t>304219</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>309554</t>
+          <t>309613</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>162536</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
